--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:22</t>
+    <t xml:space="preserve">2026-09-10 01:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:36</t>
+    <t xml:space="preserve">2026-09-18 11:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:32</t>
+    <t xml:space="preserve">2026-09-23 15:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_o_higgins.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Litueche</t>
   </si>
   <si>
-    <t xml:space="preserve">Marchihue</t>
+    <t xml:space="preserve">Marchigüe</t>
   </si>
   <si>
     <t xml:space="preserve">Navidad</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:37</t>
+    <t xml:space="preserve">2026-10-04 10:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:48</t>
+    <t xml:space="preserve">2026-10-05 16:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
